--- a/CONSOLIDATED_quantity_2026_06.xlsx
+++ b/CONSOLIDATED_quantity_2026_06.xlsx
@@ -833,7 +833,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJb</t>
+          <t>a0R3g0000080gIw</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KAIKU 1 MODULE SUBSCRIPTION</t>
+          <t>KAIKU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJq</t>
+          <t>a0R3g0000080gJb</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
+          <t>KAIKU 1 MODULE SUBSCRIPTION</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0R3g0000095FZo</t>
+          <t>a0R3g0000080gJl</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MODULE FOR RADIOTHERAPY</t>
+          <t>KAIKU SOFTWARE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0R3g0000080gJl</t>
+          <t>a0R3g0000080gJq</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KAIKU SOFTWARE</t>
+          <t>MODULE FOR RADIOTHERAPY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a0R3g0000080gIw</t>
+          <t>a0R3g0000095FZo</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -966,7 +966,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KAIKU</t>
+          <t>MODULE FOR RADIOTHERAPY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a0RQQ00000HGGi9</t>
+          <t>a0R3g0000095RL1</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>a0R3g0000095RL1</t>
+          <t>a0RQQ00000HGGi9</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>a0RQQ00000HxIaD</t>
+          <t>a0R3g0000095ROt</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a0R3g0000095ROt</t>
+          <t>a0RQQ00000HxIaD</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>a0R60000000FqrH</t>
+          <t>a0R60000000FqrO</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2958,7 +2958,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a0R60000000FqrL</t>
+          <t>a0R60000000FqrH</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2983,7 +2983,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>a0R60000000FqrO</t>
+          <t>a0R60000000FqrL</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3283,7 +3283,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>a0R60000000GdAN</t>
+          <t>a0R60000000G0mJ</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MOSAIQ IGRT Connectivity for Varian</t>
+          <t>Connectivity to DICOM RT BrainLAB iPlan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3333,7 +3333,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a0R60000000G0mJ</t>
+          <t>a0R60000000G0mL</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Connectivity to DICOM RT BrainLAB iPlan</t>
+          <t>Connectivity to Varian RapidArc VMAT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a0R60000000G0mL</t>
+          <t>a0R60000000GdAN</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Connectivity to Varian RapidArc VMAT</t>
+          <t>MOSAIQ IGRT Connectivity for Varian</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3658,7 +3658,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0U</t>
+          <t>a0R60000000Fz0K</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morphology Reference</t>
+          <t>Code Update</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3683,15 +3683,15 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0K</t>
+          <t>a0R60000000Fz0R</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Code Update</t>
+          <t>ECHART USERS FOR RO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3708,7 +3708,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0L</t>
+          <t>a0R60000000Fz0N</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>EXTENDED BARCODING</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3733,7 +3733,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0M</t>
+          <t>a0R60000000Fz0U</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TNM Staging Reference</t>
+          <t>Morphology Reference</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3758,7 +3758,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0N</t>
+          <t>a0R60000000Fz0M</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EXTENDED BARCODING</t>
+          <t>TNM Staging Reference</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3783,15 +3783,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0R</t>
+          <t>a0R60000000Fz0L</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ECHART USERS FOR RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>a0R60000000sTpI</t>
+          <t>a0R60000000sTpG</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ESI: Charge Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>a0R60000000GdDh</t>
+          <t>a0R60000000GdDq</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ESI: Charge Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>a0R60000000sTpG</t>
+          <t>a0R60000000FuUh</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3958,7 +3958,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>a0R60000000GdDq</t>
+          <t>a0R60000000sTpI</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>ESI: Charge Export to TBD</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>a0R60000000FuUe</t>
+          <t>a0R60000000GdDh</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4008,7 +4008,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>a0R60000000FuUh</t>
+          <t>a0R60000000FuUe</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>ESI: Charge Export to TBD</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>a0RQQ00000KdjWP</t>
+          <t>a0RKf00000KeXnA</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4083,7 +4083,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>a0RKf00000KeXnA</t>
+          <t>a0RQQ00000KdjWP</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4183,7 +4183,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>a0RKf00000KfaET</t>
+          <t>a0RQQ00000Izy9l</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>a0RQQ00000Izy9l</t>
+          <t>a0RKf00000KfaET</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4333,7 +4333,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>a0RQQ00000Kg4y9</t>
+          <t>a0R6g00000Hj0Ib</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4358,7 +4358,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>a0R6g00000Hj0Ib</t>
+          <t>a0RQQ00000Kg4y9</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4558,7 +4558,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>a0RQQ00000HWUnZ</t>
+          <t>a0R3g00000AS80n</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>a0R3g00000AS80n</t>
+          <t>a0RQQ00000HWUnZ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5608,7 +5608,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>a0RKf00000ExomG</t>
+          <t>a0RQQ00000KkKY5</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5633,7 +5633,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>a0RQQ00000KkKY5</t>
+          <t>a0RKf00000ExomG</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>a0RKf00000ExrOW</t>
+          <t>a0R3g0000095N75</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5783,7 +5783,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>a0R3g0000095N75</t>
+          <t>a0RKf00000ExrOW</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6483,7 +6483,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4g</t>
+          <t>a0R60000000GdjZ</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>IQ Server</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>a0R60000000GdjZ</t>
+          <t>a0R60000000Fr4h</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6533,7 +6533,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4h</t>
+          <t>a0R60000000Fr4i</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6558,7 +6558,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4i</t>
+          <t>a0R60000000Gdjc</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6583,7 +6583,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>a0R60000000Gdjc</t>
+          <t>a0R60000000Fr4g</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>IQ Server</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7108,7 +7108,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>a0R60000004SFOV</t>
+          <t>a0R60000004SFPs</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>Connectivity to DICOM RT Elekta ERGO++</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>a0R60000004SFOf</t>
+          <t>a0R60000004SFQ7</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ESI IMPLEMENTATION SERVICES</t>
+          <t>Connectivity to non-DICOM from Varian PortalVision</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7158,7 +7158,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>a0R60000004SFP4</t>
+          <t>a0R60000004SFOV</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ESI: Schedule Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>a0R60000004SFPs</t>
+          <t>a0R60000004SFP4</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Connectivity to DICOM RT Elekta ERGO++</t>
+          <t>ESI: Schedule Export to TBD</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7208,7 +7208,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>a0R60000004SFQ7</t>
+          <t>a0R60000004SFOf</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Connectivity to non-DICOM from Varian PortalVision</t>
+          <t>ESI IMPLEMENTATION SERVICES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>a0R32000003IC7d</t>
+          <t>a0R32000003IC9e</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>IQ Server</t>
+          <t>Connectivity to Elekta VMAT</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7333,7 +7333,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>a0R32000003IC9e</t>
+          <t>a0R32000003IC7d</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Connectivity to Elekta VMAT</t>
+          <t>IQ Server</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -8158,7 +8158,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>a0RQQ00000JV3eb</t>
+          <t>a0RQQ00000JQegP</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>a0RQQ00000JQegP</t>
+          <t>a0RQQ00000JV3eb</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8258,7 +8258,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>a0R60000000Fun1</t>
+          <t>a0R60000000Fun5</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>EXTENDED BARCODING</t>
+          <t>Code Update</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8283,7 +8283,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>a0R60000000Fun2</t>
+          <t>a0R60000000FunD</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Photos &amp; Diagrams</t>
+          <t>Document Management Package for RO</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>a0R60000000Fun3</t>
+          <t>a0R60000000Fun1</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>TNM Staging Reference</t>
+          <t>EXTENDED BARCODING</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>a0R60000000Fun4</t>
+          <t>a0R60000000Fun2</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>Photos &amp; Diagrams</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8358,7 +8358,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>a0R60000000Fun5</t>
+          <t>a0R60000000Fun3</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Code Update</t>
+          <t>TNM Staging Reference</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8383,7 +8383,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>a0R60000000FunD</t>
+          <t>a0R60000000Fun4</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Document Management Package for RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8533,7 +8533,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>a0R60000000G153</t>
+          <t>a0R60000000G15F</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>Document Management Package for RO</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>a0R60000000G156</t>
+          <t>a0R60000000G15E</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>PhAST Note</t>
+          <t>ECHART USERS FOR RO</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8583,7 +8583,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>a0R60000000G15E</t>
+          <t>a0R60000000G156</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>ECHART USERS FOR RO</t>
+          <t>PhAST Note</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8608,7 +8608,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>a0R60000000G15F</t>
+          <t>a0R60000000G153</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Document Management Package for RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8983,7 +8983,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>a0R60000000FuxK</t>
+          <t>a0R60000000FuxL</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>One-time TX Detail Import</t>
+          <t>One time Diagnosis Detail  Import</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9008,7 +9008,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>a0R60000000FuxL</t>
+          <t>a0R60000000FuxK</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>One time Diagnosis Detail  Import</t>
+          <t>One-time TX Detail Import</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9733,7 +9733,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>a0RQQ00000HEosn</t>
+          <t>a0RQQ00000HEpFN</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9758,7 +9758,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>a0RQQ00000HEpFN</t>
+          <t>a0RQQ00000HEosn</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10083,7 +10083,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>a0RQQ00000IyBr3</t>
+          <t>a0RQQ00000Iy4kn</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>MOSAIQ Oncology Analytics</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10108,7 +10108,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>a0RQQ00000Iy4kn</t>
+          <t>a0RQQ00000IyBr3</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Oncology Analytics</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -11508,7 +11508,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>a0RQQ00000InIO1</t>
+          <t>a0RKf00000KfTyQ</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -11533,7 +11533,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>a0RKf00000KfTyQ</t>
+          <t>a0RQQ00000InIO1</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12958,7 +12958,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>a0RKf00000ExqhY</t>
+          <t>a0RQQ00000J1sBV</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -12983,7 +12983,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>a0RQQ00000J1sBV</t>
+          <t>a0RKf00000ExqhY</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -14208,7 +14208,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>a0RKf00000KfYgR</t>
+          <t>a0RQQ00000HdoKv</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA PREMIUM USER LICENSE SUBSC</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -14233,7 +14233,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>a0RQQ00000Hdo6P</t>
+          <t>a0RQQ00000IaqP7</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>MOSAIQ Oncology Analytics</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -14258,7 +14258,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>a0RQQ00000HdoKv</t>
+          <t>a0RQQ00000Hdo6P</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>MOA PREMIUM USER LICENSE SUBSC</t>
+          <t>MOSAIQ Oncology Analytics</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>a0RQQ00000IaqP7</t>
+          <t>a0RKf00000KfYgR</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -14383,7 +14383,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>a0R60000000GbQz</t>
+          <t>a0R60000000GbN2</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Formulary Plus Canadian Version</t>
+          <t>Connectivity to Varian Truebeam 4D</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -14408,7 +14408,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>a0R60000000GbN2</t>
+          <t>a0R60000000GbQz</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Connectivity to Varian Truebeam 4D</t>
+          <t>Formulary Plus Canadian Version</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -14433,7 +14433,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>a0RQQ00000JWhV7</t>
+          <t>a0RQQ00000LDoNt</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -14458,7 +14458,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>a0RQQ00000HuIGb</t>
+          <t>a0RQQ00000JWhV7</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -14483,7 +14483,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>a0RQQ00000LDoNt</t>
+          <t>a0RQQ00000HuIGb</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
